--- a/Convert_from_xlsx_to_Json/table_normalization/employment-table19.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/employment-table19.xlsx
@@ -1058,10 +1058,10 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1376,14 +1376,14 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1">
+      <c r="B1" s="2">
         <v>2023</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3"/>
@@ -1407,13 +1407,13 @@
       <c r="D3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F3" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
